--- a/Data/National Accounts/PSA-03DEQ_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-03DEQ_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08234DE-1A4C-4C53-A932-29F7BC310FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497D35EE-72A7-431A-973B-4E2CB5D92BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DEQ" sheetId="1" r:id="rId1"/>
@@ -258,9 +258,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -268,6 +265,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -405,15 +405,7 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 2 2" xfId="4" xr:uid="{83072B31-956C-4891-99BB-453C7D1A8247}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -725,7 +717,7 @@
     </row>
     <row r="3" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:94" x14ac:dyDescent="0.2">
@@ -735,7 +727,7 @@
     </row>
     <row r="6" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:94" x14ac:dyDescent="0.2">
@@ -937,10 +929,10 @@
         <v>210523.32919050124</v>
       </c>
       <c r="Z12" s="8">
-        <v>215954.55702907965</v>
+        <v>216407.18644218409</v>
       </c>
       <c r="AA12" s="8">
-        <v>230659.94129716812</v>
+        <v>232409.25157621241</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -1087,10 +1079,10 @@
         <v>15090.171384782709</v>
       </c>
       <c r="Z13" s="11">
-        <v>14205.728076599577</v>
+        <v>14211.845868788572</v>
       </c>
       <c r="AA13" s="11">
-        <v>17769.753790109196</v>
+        <v>17864.560471144789</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -1237,10 +1229,10 @@
         <v>43130.188759093107</v>
       </c>
       <c r="Z14" s="11">
-        <v>41326.850915300281</v>
+        <v>41413.771078486403</v>
       </c>
       <c r="AA14" s="11">
-        <v>42612.699746040307</v>
+        <v>42986.591489446058</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -1387,10 +1379,10 @@
         <v>3385.5228856434037</v>
       </c>
       <c r="Z15" s="11">
-        <v>3486.8644421907211</v>
+        <v>3532.7222811293559</v>
       </c>
       <c r="AA15" s="11">
-        <v>4472.8653470691297</v>
+        <v>4574.5983347616057</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -1537,10 +1529,10 @@
         <v>2040.7346634402234</v>
       </c>
       <c r="Z16" s="11">
-        <v>3088.5241726416871</v>
+        <v>3102.3338360788198</v>
       </c>
       <c r="AA16" s="11">
-        <v>3324.2375192632271</v>
+        <v>3343.157074312036</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -1687,10 +1679,10 @@
         <v>12799.183406381009</v>
       </c>
       <c r="Z17" s="11">
-        <v>10547.421493688655</v>
+        <v>10580.066980647121</v>
       </c>
       <c r="AA17" s="11">
-        <v>12929.57501649189</v>
+        <v>13020.908356658001</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -1837,10 +1829,10 @@
         <v>99500.494076860137</v>
       </c>
       <c r="Z18" s="11">
-        <v>104012.32739671794</v>
+        <v>103972.35036045854</v>
       </c>
       <c r="AA18" s="11">
-        <v>103248.49801227287</v>
+        <v>103331.36320995107</v>
       </c>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
@@ -1987,10 +1979,10 @@
         <v>4391.9136997573205</v>
       </c>
       <c r="Z19" s="11">
-        <v>5062.020651701283</v>
+        <v>5069.5792399029133</v>
       </c>
       <c r="AA19" s="11">
-        <v>6203.1357020780588</v>
+        <v>6228.732841088713</v>
       </c>
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
@@ -2137,10 +2129,10 @@
         <v>30185.120314543332</v>
       </c>
       <c r="Z20" s="11">
-        <v>34224.819880239505</v>
+        <v>34524.516796692398</v>
       </c>
       <c r="AA20" s="11">
-        <v>40099.176163843447</v>
+        <v>41059.339798850109</v>
       </c>
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
@@ -2287,10 +2279,10 @@
         <v>250336.73743927098</v>
       </c>
       <c r="Z21" s="8">
-        <v>263522.77394919586</v>
+        <v>263580.58565614745</v>
       </c>
       <c r="AA21" s="8">
-        <v>275666.74174753076</v>
+        <v>277658.00079794711</v>
       </c>
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
@@ -2437,10 +2429,10 @@
         <v>42616.738227949878</v>
       </c>
       <c r="Z22" s="11">
-        <v>51072.773765695834</v>
+        <v>51072.48364966939</v>
       </c>
       <c r="AA22" s="11">
-        <v>47898.365499980078</v>
+        <v>48176.067498935721</v>
       </c>
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
@@ -2587,10 +2579,10 @@
         <v>26818.019033281351</v>
       </c>
       <c r="Z23" s="11">
-        <v>29027.793876810487</v>
+        <v>29005.756038374679</v>
       </c>
       <c r="AA23" s="11">
-        <v>31341.620077817148</v>
+        <v>31571.053543883347</v>
       </c>
       <c r="AB23" s="9"/>
       <c r="AC23" s="9"/>
@@ -2737,10 +2729,10 @@
         <v>100013.36470742949</v>
       </c>
       <c r="Z24" s="11">
-        <v>95048.061801988821</v>
+        <v>95069.379624397436</v>
       </c>
       <c r="AA24" s="11">
-        <v>96586.025475088041</v>
+        <v>97043.173673436133</v>
       </c>
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
@@ -2887,10 +2879,10 @@
         <v>80888.615470610268</v>
       </c>
       <c r="Z25" s="11">
-        <v>88374.1445047007</v>
+        <v>88432.96634370595</v>
       </c>
       <c r="AA25" s="11">
-        <v>99840.730694645521</v>
+        <v>100867.70608169191</v>
       </c>
       <c r="AB25" s="9"/>
       <c r="AC25" s="9"/>
@@ -3037,10 +3029,10 @@
         <v>764173.11633817758</v>
       </c>
       <c r="Z26" s="8">
-        <v>772713.25271270145</v>
+        <v>773354.32242453401</v>
       </c>
       <c r="AA26" s="8">
-        <v>820230.24493764585</v>
+        <v>822474.05571967084</v>
       </c>
       <c r="AB26" s="9"/>
       <c r="AC26" s="9"/>
@@ -3187,10 +3179,10 @@
         <v>672228.79121549509</v>
       </c>
       <c r="Z27" s="11">
-        <v>672125.52533686941</v>
+        <v>672732.30898734322</v>
       </c>
       <c r="AA27" s="11">
-        <v>734225.81844809372</v>
+        <v>736378.8530113576</v>
       </c>
       <c r="AB27" s="9"/>
       <c r="AC27" s="9"/>
@@ -3337,10 +3329,10 @@
         <v>1229.2723320173461</v>
       </c>
       <c r="Z28" s="11">
-        <v>11399.459981060427</v>
+        <v>11399.459980963575</v>
       </c>
       <c r="AA28" s="11">
-        <v>967.48816192991376</v>
+        <v>968.05235518999234</v>
       </c>
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
@@ -3487,10 +3479,10 @@
         <v>60118.521939533122</v>
       </c>
       <c r="Z29" s="11">
-        <v>78126.653710682673</v>
+        <v>78126.237499979034</v>
       </c>
       <c r="AA29" s="11">
-        <v>54190.600224727743</v>
+        <v>54225.155808497948</v>
       </c>
       <c r="AB29" s="9"/>
       <c r="AC29" s="9"/>
@@ -3637,10 +3629,10 @@
         <v>30596.530851132033</v>
       </c>
       <c r="Z30" s="11">
-        <v>11061.613684088932</v>
+        <v>11096.315956248231</v>
       </c>
       <c r="AA30" s="11">
-        <v>30846.338102894453</v>
+        <v>30901.994544625315</v>
       </c>
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
@@ -3787,10 +3779,10 @@
         <v>257576.9573706488</v>
       </c>
       <c r="Z31" s="8">
-        <v>272365.88177931251</v>
+        <v>272225.79737616796</v>
       </c>
       <c r="AA31" s="8">
-        <v>302992.52694642113</v>
+        <v>303591.20895297191</v>
       </c>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
@@ -3937,10 +3929,10 @@
         <v>23907.294964309072</v>
       </c>
       <c r="Z32" s="11">
-        <v>23999.448871735796</v>
+        <v>23972.650751627298</v>
       </c>
       <c r="AA32" s="11">
-        <v>32126.306215130615</v>
+        <v>32307.437311021695</v>
       </c>
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
@@ -4087,10 +4079,10 @@
         <v>43063.1457463478</v>
       </c>
       <c r="Z33" s="11">
-        <v>53524.104869696173</v>
+        <v>53571.684108294816</v>
       </c>
       <c r="AA33" s="11">
-        <v>47324.923227742642</v>
+        <v>47557.22974702873</v>
       </c>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
@@ -4237,10 +4229,10 @@
         <v>136790.40963171292</v>
       </c>
       <c r="Z34" s="11">
-        <v>136773.02919710852</v>
+        <v>136618.83049695473</v>
       </c>
       <c r="AA34" s="11">
-        <v>161737.4212168068</v>
+        <v>162688.53918714414</v>
       </c>
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
@@ -4387,10 +4379,10 @@
         <v>53816.107028279032</v>
       </c>
       <c r="Z35" s="11">
-        <v>58069.298840772011</v>
+        <v>58062.632019291086</v>
       </c>
       <c r="AA35" s="11">
-        <v>61803.876286741026</v>
+        <v>61038.002707777356</v>
       </c>
       <c r="AB35" s="9"/>
       <c r="AC35" s="9"/>
@@ -4632,10 +4624,10 @@
         <v>1482610.1403385985</v>
       </c>
       <c r="Z37" s="13">
-        <v>1524556.4654702893</v>
+        <v>1525567.8918990334</v>
       </c>
       <c r="AA37" s="13">
-        <v>1629549.454928766</v>
+        <v>1636132.5170468024</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -4941,7 +4933,7 @@
     </row>
     <row r="44" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:94" x14ac:dyDescent="0.2">
@@ -4951,7 +4943,7 @@
     </row>
     <row r="47" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:94" x14ac:dyDescent="0.2">
@@ -5153,10 +5145,10 @@
         <v>180224.17004580481</v>
       </c>
       <c r="Z53" s="8">
-        <v>182596.42988215672</v>
+        <v>183056.06148569356</v>
       </c>
       <c r="AA53" s="8">
-        <v>189502.11141711482</v>
+        <v>190916.18277067912</v>
       </c>
       <c r="AB53" s="9"/>
       <c r="AC53" s="9"/>
@@ -5303,10 +5295,10 @@
         <v>12805.398413954244</v>
       </c>
       <c r="Z54" s="11">
-        <v>11105.87878576653</v>
+        <v>11112.59419454317</v>
       </c>
       <c r="AA54" s="11">
-        <v>12943.976723531921</v>
+        <v>13044.146475533975</v>
       </c>
       <c r="AB54" s="9"/>
       <c r="AC54" s="9"/>
@@ -5453,10 +5445,10 @@
         <v>32756.891704327238</v>
       </c>
       <c r="Z55" s="11">
-        <v>31905.214688160326</v>
+        <v>31973.38469562852</v>
       </c>
       <c r="AA55" s="11">
-        <v>31805.620683450776</v>
+        <v>32194.945053208692</v>
       </c>
       <c r="AB55" s="9"/>
       <c r="AC55" s="9"/>
@@ -5603,10 +5595,10 @@
         <v>2895.3882479681561</v>
       </c>
       <c r="Z56" s="11">
-        <v>3011.4892298247769</v>
+        <v>3058.9536969031542</v>
       </c>
       <c r="AA56" s="11">
-        <v>3510.4172863848034</v>
+        <v>3612.7062671790363</v>
       </c>
       <c r="AB56" s="9"/>
       <c r="AC56" s="9"/>
@@ -5753,10 +5745,10 @@
         <v>1625.2149239708183</v>
       </c>
       <c r="Z57" s="11">
-        <v>2293.2225647191194</v>
+        <v>2306.9681019029308</v>
       </c>
       <c r="AA57" s="11">
-        <v>2262.970614099876</v>
+        <v>2282.4137995167757</v>
       </c>
       <c r="AB57" s="9"/>
       <c r="AC57" s="9"/>
@@ -5903,10 +5895,10 @@
         <v>10238.1614174594</v>
       </c>
       <c r="Z58" s="11">
-        <v>8308.5214859054868</v>
+        <v>8343.4283657262549</v>
       </c>
       <c r="AA58" s="11">
-        <v>9577.021459909136</v>
+        <v>9673.0008578108991</v>
       </c>
       <c r="AB58" s="9"/>
       <c r="AC58" s="9"/>
@@ -6053,10 +6045,10 @@
         <v>89759.548686591239</v>
       </c>
       <c r="Z59" s="11">
-        <v>91948.240515305821</v>
+        <v>91917.578951596064</v>
       </c>
       <c r="AA59" s="11">
-        <v>91249.914327989638</v>
+        <v>91115.454133491934</v>
       </c>
       <c r="AB59" s="9"/>
       <c r="AC59" s="9"/>
@@ -6203,10 +6195,10 @@
         <v>3550.0347252617994</v>
       </c>
       <c r="Z60" s="11">
-        <v>4225.407975211192</v>
+        <v>4233.2172624881623</v>
       </c>
       <c r="AA60" s="11">
-        <v>4621.3090846481145</v>
+        <v>4647.3651354629837</v>
       </c>
       <c r="AB60" s="9"/>
       <c r="AC60" s="9"/>
@@ -6353,10 +6345,10 @@
         <v>26593.531926271913</v>
       </c>
       <c r="Z61" s="11">
-        <v>29798.454637263458</v>
+        <v>30109.93621690532</v>
       </c>
       <c r="AA61" s="11">
-        <v>33530.881237100548</v>
+        <v>34346.151048474829</v>
       </c>
       <c r="AB61" s="9"/>
       <c r="AC61" s="9"/>
@@ -6503,10 +6495,10 @@
         <v>215072.54256610075</v>
       </c>
       <c r="Z62" s="8">
-        <v>220610.25141162949</v>
+        <v>220644.4247615395</v>
       </c>
       <c r="AA62" s="8">
-        <v>225918.97357224859</v>
+        <v>227869.12437278737</v>
       </c>
       <c r="AB62" s="9"/>
       <c r="AC62" s="9"/>
@@ -6653,10 +6645,10 @@
         <v>35061.98716418304</v>
       </c>
       <c r="Z63" s="11">
-        <v>40976.996909762172</v>
+        <v>40979.117093192588</v>
       </c>
       <c r="AA63" s="11">
-        <v>37137.182192159162</v>
+        <v>37394.243360558365</v>
       </c>
       <c r="AB63" s="9"/>
       <c r="AC63" s="9"/>
@@ -6803,10 +6795,10 @@
         <v>21749.097518746974</v>
       </c>
       <c r="Z64" s="11">
-        <v>22874.992103278953</v>
+        <v>22860.340480689087</v>
       </c>
       <c r="AA64" s="11">
-        <v>23800.699180466734</v>
+        <v>23975.902355023172</v>
       </c>
       <c r="AB64" s="9"/>
       <c r="AC64" s="9"/>
@@ -6953,10 +6945,10 @@
         <v>82223.235300435015</v>
       </c>
       <c r="Z65" s="11">
-        <v>74826.896892775942</v>
+        <v>74819.275965360503</v>
       </c>
       <c r="AA65" s="11">
-        <v>76764.311952497053</v>
+        <v>77175.619655139657</v>
       </c>
       <c r="AB65" s="9"/>
       <c r="AC65" s="9"/>
@@ -7103,10 +7095,10 @@
         <v>76038.222582735732</v>
       </c>
       <c r="Z66" s="11">
-        <v>81931.365505812428</v>
+        <v>81985.691222297319</v>
       </c>
       <c r="AA66" s="11">
-        <v>88216.780247125658</v>
+        <v>89323.359002066165</v>
       </c>
       <c r="AB66" s="9"/>
       <c r="AC66" s="9"/>
@@ -7253,10 +7245,10 @@
         <v>704939.52107477409</v>
       </c>
       <c r="Z67" s="8">
-        <v>684679.19099006441</v>
+        <v>685175.3548784937</v>
       </c>
       <c r="AA67" s="8">
-        <v>718920.55866227834</v>
+        <v>721182.46843629249</v>
       </c>
       <c r="AB67" s="9"/>
       <c r="AC67" s="9"/>
@@ -7403,10 +7395,10 @@
         <v>631134.3694199177</v>
       </c>
       <c r="Z68" s="11">
-        <v>610159.92901837616</v>
+        <v>610630.5913863047</v>
       </c>
       <c r="AA68" s="11">
-        <v>655758.91287340771</v>
+        <v>657957.6607273079</v>
       </c>
       <c r="AB68" s="9"/>
       <c r="AC68" s="9"/>
@@ -7553,10 +7545,10 @@
         <v>895.48174924477485</v>
       </c>
       <c r="Z69" s="11">
-        <v>9020.1486802020863</v>
+        <v>9020.1486801177925</v>
       </c>
       <c r="AA69" s="11">
-        <v>743.86072028897388</v>
+        <v>744.23132438393861</v>
       </c>
       <c r="AB69" s="9"/>
       <c r="AC69" s="9"/>
@@ -7703,10 +7695,10 @@
         <v>47438.923926202391</v>
       </c>
       <c r="Z70" s="11">
-        <v>56799.460445523328</v>
+        <v>56799.112352731347</v>
       </c>
       <c r="AA70" s="11">
-        <v>37548.991156807031</v>
+        <v>37574.467559947705</v>
       </c>
       <c r="AB70" s="9"/>
       <c r="AC70" s="9"/>
@@ -7853,10 +7845,10 @@
         <v>25470.745979409323</v>
       </c>
       <c r="Z71" s="11">
-        <v>8699.6528459627825</v>
+        <v>8725.5024593399103</v>
       </c>
       <c r="AA71" s="11">
-        <v>24868.793911774683</v>
+        <v>24906.10882465286</v>
       </c>
       <c r="AB71" s="9"/>
       <c r="AC71" s="9"/>
@@ -8003,10 +7995,10 @@
         <v>222611.90377261001</v>
       </c>
       <c r="Z72" s="8">
-        <v>228763.31405664555</v>
+        <v>228666.00015132103</v>
       </c>
       <c r="AA72" s="8">
-        <v>243489.21019055721</v>
+        <v>243655.585172944</v>
       </c>
       <c r="AB72" s="9"/>
       <c r="AC72" s="9"/>
@@ -8153,10 +8145,10 @@
         <v>20102.018156496088</v>
       </c>
       <c r="Z73" s="11">
-        <v>20332.578488787141</v>
+        <v>20313.843564498595</v>
       </c>
       <c r="AA73" s="11">
-        <v>25969.059827788431</v>
+        <v>26048.878354369201</v>
       </c>
       <c r="AB73" s="9"/>
       <c r="AC73" s="9"/>
@@ -8303,10 +8295,10 @@
         <v>41603.888785075804</v>
       </c>
       <c r="Z74" s="11">
-        <v>50359.957655373306</v>
+        <v>50401.306529578789</v>
       </c>
       <c r="AA74" s="11">
-        <v>45509.255013988033</v>
+        <v>45673.767201187286</v>
       </c>
       <c r="AB74" s="9"/>
       <c r="AC74" s="9"/>
@@ -8453,10 +8445,10 @@
         <v>115763.6181716791</v>
       </c>
       <c r="Z75" s="11">
-        <v>110995.91117142486</v>
+        <v>110883.1216128706</v>
       </c>
       <c r="AA75" s="11">
-        <v>122027.55023394919</v>
+        <v>122589.37969956653</v>
       </c>
       <c r="AB75" s="9"/>
       <c r="AC75" s="9"/>
@@ -8603,10 +8595,10 @@
         <v>45142.378659358998</v>
       </c>
       <c r="Z76" s="11">
-        <v>47074.866741060236</v>
+        <v>47067.728444373039</v>
       </c>
       <c r="AA76" s="11">
-        <v>49983.345114831558</v>
+        <v>49343.559917820967</v>
       </c>
       <c r="AB76" s="9"/>
       <c r="AC76" s="9"/>
@@ -8848,10 +8840,10 @@
         <v>1322848.1374592895</v>
       </c>
       <c r="Z78" s="13">
-        <v>1316649.1863404962</v>
+        <v>1317541.8412770478</v>
       </c>
       <c r="AA78" s="13">
-        <v>1377830.8538421991</v>
+        <v>1383623.3607527029</v>
       </c>
       <c r="AB78" s="9"/>
       <c r="AC78" s="9"/>
@@ -9159,7 +9151,7 @@
     </row>
     <row r="85" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:94" x14ac:dyDescent="0.2">
@@ -9169,7 +9161,7 @@
     </row>
     <row r="88" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:94" x14ac:dyDescent="0.2">
@@ -9285,7 +9277,7 @@
         <v>70</v>
       </c>
       <c r="Z92" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AA92" s="16"/>
     </row>
@@ -9366,10 +9358,10 @@
         <v>0.63368191932345042</v>
       </c>
       <c r="Y94" s="19">
-        <v>2.5798698222483978</v>
+        <v>2.7948718435658861</v>
       </c>
       <c r="Z94" s="19">
-        <v>6.8094808789370944</v>
+        <v>7.3944240933530523</v>
       </c>
       <c r="AA94" s="19"/>
       <c r="AB94" s="9"/>
@@ -9508,10 +9500,10 @@
         <v>40.274832498896018</v>
       </c>
       <c r="Y95" s="19">
-        <v>-5.8610554223063787</v>
+        <v>-5.8205138536720682</v>
       </c>
       <c r="Z95" s="19">
-        <v>25.08865222741008</v>
+        <v>25.701901329919053</v>
       </c>
       <c r="AA95" s="19"/>
       <c r="AB95" s="9"/>
@@ -9650,10 +9642,10 @@
         <v>3.873521140173537</v>
       </c>
       <c r="Y96" s="19">
-        <v>-4.181149899124037</v>
+        <v>-3.9796201454018245</v>
       </c>
       <c r="Z96" s="19">
-        <v>3.1114125617153405</v>
+        <v>3.7978198314248601</v>
       </c>
       <c r="AA96" s="19"/>
       <c r="AB96" s="9"/>
@@ -9792,10 +9784,10 @@
         <v>12.626615134121892</v>
       </c>
       <c r="Y97" s="19">
-        <v>2.9933797516792851</v>
+        <v>4.3479072644927044</v>
       </c>
       <c r="Z97" s="19">
-        <v>28.277580652344653</v>
+        <v>29.492158474998433</v>
       </c>
       <c r="AA97" s="19"/>
       <c r="AB97" s="9"/>
@@ -9934,10 +9926,10 @@
         <v>3.3073015626765141</v>
       </c>
       <c r="Y98" s="19">
-        <v>51.343740466245833</v>
+        <v>52.020441052781308</v>
       </c>
       <c r="Z98" s="19">
-        <v>7.6319087514192603</v>
+        <v>7.7626474440804856</v>
       </c>
       <c r="AA98" s="19"/>
       <c r="AB98" s="9"/>
@@ -10076,10 +10068,10 @@
         <v>2.4485243955150366</v>
       </c>
       <c r="Y99" s="19">
-        <v>-17.593012313346051</v>
+        <v>-17.33795317463418</v>
       </c>
       <c r="Z99" s="19">
-        <v>22.585174245939285</v>
+        <v>23.0701883123767</v>
       </c>
       <c r="AA99" s="19"/>
       <c r="AB99" s="9"/>
@@ -10218,10 +10210,10 @@
         <v>-0.30886424386173417</v>
       </c>
       <c r="Y100" s="19">
-        <v>4.5344833326883816</v>
+        <v>4.4943056063059004</v>
       </c>
       <c r="Z100" s="19">
-        <v>-0.73436428504452067</v>
+        <v>-0.6164977018267308</v>
       </c>
       <c r="AA100" s="19"/>
       <c r="AB100" s="9"/>
@@ -10360,10 +10352,10 @@
         <v>39.481285854855258</v>
       </c>
       <c r="Y101" s="19">
-        <v>15.257744066805998</v>
+        <v>15.429846451287005</v>
       </c>
       <c r="Z101" s="19">
-        <v>22.542678682933868</v>
+        <v>22.864887722082401</v>
       </c>
       <c r="AA101" s="19"/>
       <c r="AB101" s="9"/>
@@ -10502,10 +10494,10 @@
         <v>-17.269542262718815</v>
       </c>
       <c r="Y102" s="19">
-        <v>13.383082537358064</v>
+        <v>14.37594562132098</v>
       </c>
       <c r="Z102" s="19">
-        <v>17.164023957349258</v>
+        <v>18.928065063560211</v>
       </c>
       <c r="AA102" s="19"/>
       <c r="AB102" s="9"/>
@@ -10644,10 +10636,10 @@
         <v>11.00869227109888</v>
       </c>
       <c r="Y103" s="19">
-        <v>5.2673197888598651</v>
+        <v>5.2904133657527126</v>
       </c>
       <c r="Z103" s="19">
-        <v>4.6083181412913206</v>
+        <v>5.3408391618661426</v>
       </c>
       <c r="AA103" s="19"/>
       <c r="AB103" s="9"/>
@@ -10786,10 +10778,10 @@
         <v>4.5907276846822498</v>
       </c>
       <c r="Y104" s="19">
-        <v>19.842052417329597</v>
+        <v>19.841371661273399</v>
       </c>
       <c r="Z104" s="19">
-        <v>-6.2154608642930498</v>
+        <v>-5.671187190741648</v>
       </c>
       <c r="AA104" s="19"/>
       <c r="AB104" s="9"/>
@@ -10928,10 +10920,10 @@
         <v>12.401851714865202</v>
       </c>
       <c r="Y105" s="19">
-        <v>8.239888415273299</v>
+        <v>8.1577129256949661</v>
       </c>
       <c r="Z105" s="19">
-        <v>7.9710714869555233</v>
+        <v>8.844098054588784</v>
       </c>
       <c r="AA105" s="19"/>
       <c r="AB105" s="9"/>
@@ -11070,10 +11062,10 @@
         <v>35.627418783188659</v>
       </c>
       <c r="Y106" s="19">
-        <v>-4.9646393959104813</v>
+        <v>-4.9433244221857393</v>
       </c>
       <c r="Z106" s="19">
-        <v>1.6180905154102163</v>
+        <v>2.0761617008933939</v>
       </c>
       <c r="AA106" s="19"/>
       <c r="AB106" s="9"/>
@@ -11212,10 +11204,10 @@
         <v>-7.1999707690630004</v>
       </c>
       <c r="Y107" s="19">
-        <v>9.2541193721014992</v>
+        <v>9.326838924368559</v>
       </c>
       <c r="Z107" s="19">
-        <v>12.975046326287099</v>
+        <v>14.061203928924854</v>
       </c>
       <c r="AA107" s="19"/>
       <c r="AB107" s="9"/>
@@ -11354,10 +11346,10 @@
         <v>20.629170832889287</v>
       </c>
       <c r="Y108" s="19">
-        <v>1.1175656656762669</v>
+        <v>1.2014563048686711</v>
       </c>
       <c r="Z108" s="19">
-        <v>6.1493693887260719</v>
+        <v>6.3515172632826449</v>
       </c>
       <c r="AA108" s="19"/>
       <c r="AB108" s="9"/>
@@ -11496,10 +11488,10 @@
         <v>20.013818476521863</v>
       </c>
       <c r="Y109" s="19">
-        <v>-1.5361716126278679E-2</v>
+        <v>7.4902738238506572E-2</v>
       </c>
       <c r="Z109" s="19">
-        <v>9.2393891870271858</v>
+        <v>9.4609019328684809</v>
       </c>
       <c r="AA109" s="19"/>
       <c r="AB109" s="9"/>
@@ -11638,10 +11630,10 @@
         <v>-52.959402187682279</v>
       </c>
       <c r="Y110" s="19">
-        <v>827.33397508043572</v>
+        <v>827.33397507255688</v>
       </c>
       <c r="Z110" s="19">
-        <v>-91.512859700921425</v>
+        <v>-91.507910402715723</v>
       </c>
       <c r="AA110" s="19"/>
       <c r="AB110" s="9"/>
@@ -11780,10 +11772,10 @@
         <v>57.70904226584446</v>
       </c>
       <c r="Y111" s="19">
-        <v>29.954382094193932</v>
+        <v>29.953689777266931</v>
       </c>
       <c r="Z111" s="19">
-        <v>-30.637499942842211</v>
+        <v>-30.592899973568422</v>
       </c>
       <c r="AA111" s="19"/>
       <c r="AB111" s="9"/>
@@ -11922,10 +11914,10 @@
         <v>-6.2325267925914147</v>
       </c>
       <c r="Y112" s="19">
-        <v>-63.846836957073954</v>
+        <v>-63.73341798049735</v>
       </c>
       <c r="Z112" s="19">
-        <v>178.85929651714332</v>
+        <v>178.48877651347601</v>
       </c>
       <c r="AA112" s="19"/>
       <c r="AB112" s="9"/>
@@ -12064,10 +12056,10 @@
         <v>4.9285328932609218</v>
       </c>
       <c r="Y113" s="19">
-        <v>5.7415556731585724</v>
+        <v>5.6871702170313796</v>
       </c>
       <c r="Z113" s="19">
-        <v>11.244670208702658</v>
+        <v>11.521836607374311</v>
       </c>
       <c r="AA113" s="19"/>
       <c r="AB113" s="9"/>
@@ -12206,10 +12198,10 @@
         <v>4.7994434922687503</v>
       </c>
       <c r="Y114" s="19">
-        <v>0.38546354811073513</v>
+        <v>0.2733717361826109</v>
       </c>
       <c r="Z114" s="19">
-        <v>33.862683209220847</v>
+        <v>34.767897158092211</v>
       </c>
       <c r="AA114" s="19"/>
       <c r="AB114" s="9"/>
@@ -12348,10 +12340,10 @@
         <v>14.809540473857481</v>
       </c>
       <c r="Y115" s="19">
-        <v>24.292138769810066</v>
+        <v>24.402625910900284</v>
       </c>
       <c r="Z115" s="19">
-        <v>-11.582037022469351</v>
+        <v>-11.226927921675752</v>
       </c>
       <c r="AA115" s="19"/>
       <c r="AB115" s="9"/>
@@ -12490,10 +12482,10 @@
         <v>3.8539550311772643</v>
       </c>
       <c r="Y116" s="19">
-        <v>-1.2705886802436339E-2</v>
+        <v>-0.12543213754541682</v>
       </c>
       <c r="Z116" s="19">
-        <v>18.252423132137551</v>
+        <v>19.082075725110599</v>
       </c>
       <c r="AA116" s="19"/>
       <c r="AB116" s="9"/>
@@ -12632,10 +12624,10 @@
         <v>0.69718407825382656</v>
       </c>
       <c r="Y117" s="19">
-        <v>7.9031948748318683</v>
+        <v>7.8908067221967713</v>
       </c>
       <c r="Z117" s="19">
-        <v>6.4312425335276657</v>
+        <v>5.1244157989560648</v>
       </c>
       <c r="AA117" s="19"/>
       <c r="AB117" s="9"/>
@@ -12863,10 +12855,10 @@
         <v>12.859601205204157</v>
       </c>
       <c r="Y119" s="20">
-        <v>2.8292215188890424</v>
+        <v>2.8974408303064934</v>
       </c>
       <c r="Z119" s="20">
-        <v>6.886789163698765</v>
+        <v>7.2474404931358123</v>
       </c>
       <c r="AA119" s="20"/>
       <c r="AB119" s="9"/>
@@ -13158,7 +13150,7 @@
     </row>
     <row r="126" spans="1:88" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="128" spans="1:88" x14ac:dyDescent="0.2">
@@ -13168,7 +13160,7 @@
     </row>
     <row r="129" spans="1:88" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="130" spans="1:88" x14ac:dyDescent="0.2">
@@ -13284,7 +13276,7 @@
         <v>70</v>
       </c>
       <c r="Z133" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AA133" s="21"/>
     </row>
@@ -13365,10 +13357,10 @@
         <v>-2.9681207881867948</v>
       </c>
       <c r="Y135" s="19">
-        <v>1.3162828469394583</v>
+        <v>1.5713161221211323</v>
       </c>
       <c r="Z135" s="19">
-        <v>3.7819367768662744</v>
+        <v>4.2938328407114028</v>
       </c>
       <c r="AA135" s="19"/>
       <c r="AB135" s="9"/>
@@ -13507,10 +13499,10 @@
         <v>36.414812224581908</v>
       </c>
       <c r="Y136" s="19">
-        <v>-13.271899657067451</v>
+        <v>-13.21945764347636</v>
       </c>
       <c r="Z136" s="19">
-        <v>16.550675306497368</v>
+        <v>17.381650469512252</v>
       </c>
       <c r="AA136" s="19"/>
       <c r="AB136" s="9"/>
@@ -13649,10 +13641,10 @@
         <v>-10.740629404155243</v>
       </c>
       <c r="Y137" s="19">
-        <v>-2.5999933811009441</v>
+        <v>-2.3918844796718446</v>
       </c>
       <c r="Z137" s="19">
-        <v>-0.3121558832403224</v>
+        <v>0.69295246558762358</v>
       </c>
       <c r="AA137" s="19"/>
       <c r="AB137" s="9"/>
@@ -13791,10 +13783,10 @@
         <v>8.1789800595304314</v>
       </c>
       <c r="Y138" s="19">
-        <v>4.0098588483977977</v>
+        <v>5.6491715420127377</v>
       </c>
       <c r="Z138" s="19">
-        <v>16.567486000574434</v>
+        <v>18.102679057760639</v>
       </c>
       <c r="AA138" s="19"/>
       <c r="AB138" s="9"/>
@@ -13933,10 +13925,10 @@
         <v>-4.9960005131146659</v>
       </c>
       <c r="Y139" s="19">
-        <v>41.102726223814557</v>
+        <v>41.948493573170879</v>
       </c>
       <c r="Z139" s="19">
-        <v>-1.319189470950846</v>
+        <v>-1.0643537882427268</v>
       </c>
       <c r="AA139" s="19"/>
       <c r="AB139" s="9"/>
@@ -14075,10 +14067,10 @@
         <v>-2.8238303469469486</v>
       </c>
       <c r="Y140" s="19">
-        <v>-18.847524012106788</v>
+        <v>-18.506575296830235</v>
       </c>
       <c r="Z140" s="19">
-        <v>15.267457346719553</v>
+        <v>15.935565499026268</v>
       </c>
       <c r="AA140" s="19"/>
       <c r="AB140" s="9"/>
@@ -14217,10 +14209,10 @@
         <v>-0.91758722589129604</v>
       </c>
       <c r="Y141" s="19">
-        <v>2.4383944223658176</v>
+        <v>2.4042347544993845</v>
       </c>
       <c r="Z141" s="19">
-        <v>-0.75947748798948567</v>
+        <v>-0.87265659871930268</v>
       </c>
       <c r="AA141" s="19"/>
       <c r="AB141" s="9"/>
@@ -14359,10 +14351,10 @@
         <v>22.960386124336281</v>
       </c>
       <c r="Y142" s="19">
-        <v>19.024412497812591</v>
+        <v>19.244390269336904</v>
       </c>
       <c r="Z142" s="19">
-        <v>9.3695357172495193</v>
+        <v>9.7832888626981855</v>
       </c>
       <c r="AA142" s="19"/>
       <c r="AB142" s="9"/>
@@ -14501,10 +14493,10 @@
         <v>-14.902482244038097</v>
       </c>
       <c r="Y143" s="19">
-        <v>12.051512073976838</v>
+        <v>13.222780262442413</v>
       </c>
       <c r="Z143" s="19">
-        <v>12.525571024645103</v>
+        <v>14.069159101011564</v>
       </c>
       <c r="AA143" s="19"/>
       <c r="AB143" s="9"/>
@@ -14643,10 +14635,10 @@
         <v>5.5222726116651586</v>
       </c>
       <c r="Y144" s="19">
-        <v>2.5748097732311663</v>
+        <v>2.5906989934460398</v>
       </c>
       <c r="Z144" s="19">
-        <v>2.4063805406366612</v>
+        <v>3.2743630930425383</v>
       </c>
       <c r="AA144" s="19"/>
       <c r="AB144" s="9"/>
@@ -14785,10 +14777,10 @@
         <v>-0.30895237681922083</v>
       </c>
       <c r="Y145" s="19">
-        <v>16.87014976613051</v>
+        <v>16.876196723539081</v>
       </c>
       <c r="Z145" s="19">
-        <v>-9.3706591677737805</v>
+        <v>-8.7480501946435112</v>
       </c>
       <c r="AA145" s="19"/>
       <c r="AB145" s="9"/>
@@ -14927,10 +14919,10 @@
         <v>5.4170077411476427</v>
       </c>
       <c r="Y146" s="19">
-        <v>5.1767416259984884</v>
+        <v>5.1093750487083867</v>
       </c>
       <c r="Z146" s="19">
-        <v>4.0468082918161343</v>
+        <v>4.8799005215011562</v>
       </c>
       <c r="AA146" s="19"/>
       <c r="AB146" s="9"/>
@@ -15069,10 +15061,10 @@
         <v>31.032774482087234</v>
       </c>
       <c r="Y147" s="19">
-        <v>-8.9954358772597942</v>
+        <v>-9.0047044585648166</v>
       </c>
       <c r="Z147" s="19">
-        <v>2.5891960513842349</v>
+        <v>3.1493805030538908</v>
       </c>
       <c r="AA147" s="19"/>
       <c r="AB147" s="9"/>
@@ -15211,10 +15203,10 @@
         <v>-10.821228292882807</v>
       </c>
       <c r="Y148" s="19">
-        <v>7.750237608019404</v>
+        <v>7.8216828820403492</v>
       </c>
       <c r="Z148" s="19">
-        <v>7.6715610712814595</v>
+        <v>8.9499370809393781</v>
       </c>
       <c r="AA148" s="19"/>
       <c r="AB148" s="9"/>
@@ -15353,10 +15345,10 @@
         <v>16.831484990699238</v>
       </c>
       <c r="Y149" s="19">
-        <v>-2.8740522383849481</v>
+        <v>-2.8036683439378294</v>
       </c>
       <c r="Z149" s="19">
-        <v>5.0010819844984695</v>
+        <v>5.2551676445198723</v>
       </c>
       <c r="AA149" s="19"/>
       <c r="AB149" s="9"/>
@@ -15495,10 +15487,10 @@
         <v>17.560079207645401</v>
       </c>
       <c r="Y150" s="19">
-        <v>-3.323292379215431</v>
+        <v>-3.2487183438382914</v>
       </c>
       <c r="Z150" s="19">
-        <v>7.4732839189212399</v>
+        <v>7.7505238041804176</v>
       </c>
       <c r="AA150" s="19"/>
       <c r="AB150" s="9"/>
@@ -15637,10 +15629,10 @@
         <v>-68.417637014787203</v>
       </c>
       <c r="Y151" s="19">
-        <v>907.29564704243671</v>
+        <v>907.29564703302367</v>
       </c>
       <c r="Z151" s="19">
-        <v>-91.753343025025302</v>
+        <v>-91.74923439982345</v>
       </c>
       <c r="AA151" s="19"/>
       <c r="AB151" s="9"/>
@@ -15779,10 +15771,10 @@
         <v>40.136097396020546</v>
       </c>
       <c r="Y152" s="19">
-        <v>19.731764012780957</v>
+        <v>19.731030242359608</v>
       </c>
       <c r="Z152" s="19">
-        <v>-33.891993229723596</v>
+        <v>-33.846734564081913</v>
       </c>
       <c r="AA152" s="19"/>
       <c r="AB152" s="9"/>
@@ -15921,10 +15913,10 @@
         <v>-14.621981832538239</v>
       </c>
       <c r="Y153" s="19">
-        <v>-65.844530611723641</v>
+        <v>-65.743043150783052</v>
       </c>
       <c r="Z153" s="19">
-        <v>185.85961247080633</v>
+        <v>185.44039659278286</v>
       </c>
       <c r="AA153" s="19"/>
       <c r="AB153" s="9"/>
@@ -16063,10 +16055,10 @@
         <v>0.37068875772972376</v>
       </c>
       <c r="Y154" s="19">
-        <v>2.7632890154513063</v>
+        <v>2.7195744145358276</v>
       </c>
       <c r="Z154" s="19">
-        <v>6.4371755561581239</v>
+        <v>6.5552312157048078</v>
       </c>
       <c r="AA154" s="19"/>
       <c r="AB154" s="9"/>
@@ -16205,10 +16197,10 @@
         <v>9.2618237990401013</v>
       </c>
       <c r="Y155" s="19">
-        <v>1.1469511692613139</v>
+        <v>1.053751948453268</v>
       </c>
       <c r="Z155" s="19">
-        <v>27.721429144413023</v>
+        <v>28.232150019572941</v>
       </c>
       <c r="AA155" s="19"/>
       <c r="AB155" s="9"/>
@@ -16347,10 +16339,10 @@
         <v>15.261556549689104</v>
       </c>
       <c r="Y156" s="19">
-        <v>21.046275062244874</v>
+        <v>21.145662103728171</v>
       </c>
       <c r="Z156" s="19">
-        <v>-9.6320625894484095</v>
+        <v>-9.3797951956207157</v>
       </c>
       <c r="AA156" s="19"/>
       <c r="AB156" s="9"/>
@@ -16489,10 +16481,10 @@
         <v>-3.0136685361423758</v>
       </c>
       <c r="Y157" s="19">
-        <v>-4.1184847843850747</v>
+        <v>-4.2159157046825015</v>
       </c>
       <c r="Z157" s="19">
-        <v>9.9387796776466928</v>
+        <v>10.5572948492254</v>
       </c>
       <c r="AA157" s="19"/>
       <c r="AB157" s="9"/>
@@ -16631,10 +16623,10 @@
         <v>-5.8273697513344445</v>
       </c>
       <c r="Y158" s="19">
-        <v>4.2808734034235414</v>
+        <v>4.2650605532831776</v>
       </c>
       <c r="Z158" s="19">
-        <v>6.1784102114822446</v>
+        <v>4.8352269137815256</v>
       </c>
       <c r="AA158" s="19"/>
       <c r="AB158" s="9"/>
@@ -16862,10 +16854,10 @@
         <v>8.9009946503648223</v>
       </c>
       <c r="Y160" s="20">
-        <v>-0.4686064063785409</v>
+        <v>-0.40112663214941335</v>
       </c>
       <c r="Z160" s="20">
-        <v>4.6467706156225148</v>
+        <v>5.0155158193385887</v>
       </c>
       <c r="AA160" s="20"/>
       <c r="AB160" s="9"/>
@@ -17158,7 +17150,7 @@
     </row>
     <row r="166" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="168" spans="1:94" x14ac:dyDescent="0.2">
@@ -17168,7 +17160,7 @@
     </row>
     <row r="169" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="170" spans="1:94" x14ac:dyDescent="0.2">
@@ -17370,10 +17362,10 @@
         <v>116.81192879789417</v>
       </c>
       <c r="Z175" s="17">
-        <v>118.26877292642108</v>
+        <v>118.21907708808486</v>
       </c>
       <c r="AA175" s="17">
-        <v>121.71892944741943</v>
+        <v>121.73365725386051</v>
       </c>
       <c r="AB175" s="9"/>
       <c r="AC175" s="9"/>
@@ -17520,10 +17512,10 @@
         <v>117.84226384037152</v>
       </c>
       <c r="Z176" s="17">
-        <v>127.91178753729837</v>
+        <v>127.88954244155957</v>
       </c>
       <c r="AA176" s="17">
-        <v>137.28202831054307</v>
+        <v>136.9546141225272</v>
       </c>
       <c r="AB176" s="9"/>
       <c r="AC176" s="9"/>
@@ -17670,10 +17662,10 @@
         <v>131.66752556499597</v>
       </c>
       <c r="Z177" s="17">
-        <v>129.53008252483636</v>
+        <v>129.52576485951016</v>
       </c>
       <c r="AA177" s="17">
-        <v>133.97851961497079</v>
+        <v>133.51969204607113</v>
       </c>
       <c r="AB177" s="9"/>
       <c r="AC177" s="9"/>
@@ -17820,10 +17812,10 @@
         <v>116.92811449446204</v>
       </c>
       <c r="Z178" s="17">
-        <v>115.78538643465789</v>
+        <v>115.4879292454096</v>
       </c>
       <c r="AA178" s="17">
-        <v>127.4169132090704</v>
+        <v>126.62524978355513</v>
       </c>
       <c r="AB178" s="9"/>
       <c r="AC178" s="9"/>
@@ -17970,10 +17962,10 @@
         <v>125.56706398278594</v>
       </c>
       <c r="Z179" s="17">
-        <v>134.68052426128025</v>
+        <v>134.47666803541071</v>
       </c>
       <c r="AA179" s="17">
-        <v>146.89706965485644</v>
+        <v>146.47462589911774</v>
       </c>
       <c r="AB179" s="9"/>
       <c r="AC179" s="9"/>
@@ -18120,10 +18112,10 @@
         <v>125.01447168584619</v>
       </c>
       <c r="Z180" s="17">
-        <v>126.94703277329451</v>
+        <v>126.80718904603646</v>
       </c>
       <c r="AA180" s="17">
-        <v>135.00622370553361</v>
+        <v>134.61084670682814</v>
       </c>
       <c r="AB180" s="9"/>
       <c r="AC180" s="9"/>
@@ -18270,10 +18262,10 @@
         <v>110.85226645276578</v>
       </c>
       <c r="Z181" s="17">
-        <v>113.12051955948404</v>
+        <v>113.11476166622114</v>
       </c>
       <c r="AA181" s="17">
-        <v>113.14914515004956</v>
+        <v>113.40706600502895</v>
       </c>
       <c r="AB181" s="9"/>
       <c r="AC181" s="9"/>
@@ -18420,10 +18412,10 @@
         <v>123.71466871872461</v>
       </c>
       <c r="Z182" s="17">
-        <v>119.79957157742327</v>
+        <v>119.75712385059967</v>
       </c>
       <c r="AA182" s="17">
-        <v>134.22897253691031</v>
+        <v>134.02718873020484</v>
       </c>
       <c r="AB182" s="9"/>
       <c r="AC182" s="9"/>
@@ -18570,10 +18562,10 @@
         <v>113.50549599138904</v>
       </c>
       <c r="Z183" s="17">
-        <v>114.85434495465682</v>
+        <v>114.66154078834781</v>
       </c>
       <c r="AA183" s="17">
-        <v>119.58879303021523</v>
+        <v>119.54567992466039</v>
       </c>
       <c r="AB183" s="9"/>
       <c r="AC183" s="9"/>
@@ -18720,10 +18712,10 @@
         <v>116.39641883265135</v>
       </c>
       <c r="Z184" s="17">
-        <v>119.45173547601706</v>
+        <v>119.45943612262626</v>
       </c>
       <c r="AA184" s="17">
-        <v>122.0201815671639</v>
+        <v>121.84976861705343</v>
       </c>
       <c r="AB184" s="9"/>
       <c r="AC184" s="9"/>
@@ -18870,10 +18862,10 @@
         <v>121.54684224938701</v>
       </c>
       <c r="Z185" s="17">
-        <v>124.63766897844212</v>
+        <v>124.6305124962136</v>
       </c>
       <c r="AA185" s="17">
-        <v>128.97684388691434</v>
+        <v>128.83284476281048</v>
       </c>
       <c r="AB185" s="9"/>
       <c r="AC185" s="9"/>
@@ -19020,10 +19012,10 @@
         <v>123.30635333335161</v>
       </c>
       <c r="Z186" s="17">
-        <v>126.89750337727801</v>
+        <v>126.88243231931229</v>
       </c>
       <c r="AA186" s="17">
-        <v>131.68361080559876</v>
+        <v>131.67827044169172</v>
       </c>
       <c r="AB186" s="9"/>
       <c r="AC186" s="9"/>
@@ -19170,10 +19162,10 @@
         <v>121.6363772867745</v>
       </c>
       <c r="Z187" s="17">
-        <v>127.02392555204986</v>
+        <v>127.06535635069795</v>
       </c>
       <c r="AA187" s="17">
-        <v>125.82152177024261</v>
+        <v>125.74330352911312</v>
       </c>
       <c r="AB187" s="9"/>
       <c r="AC187" s="9"/>
@@ -19320,10 +19312,10 @@
         <v>106.37888777923092</v>
       </c>
       <c r="Z188" s="17">
-        <v>107.86362946487351</v>
+        <v>107.86390286559563</v>
       </c>
       <c r="AA188" s="17">
-        <v>113.17657526715116</v>
+        <v>112.9242196090708</v>
       </c>
       <c r="AB188" s="9"/>
       <c r="AC188" s="9"/>
@@ -19470,10 +19462,10 @@
         <v>108.40264923338303</v>
       </c>
       <c r="Z189" s="17">
-        <v>112.85770954939312</v>
+        <v>112.86954746959303</v>
       </c>
       <c r="AA189" s="17">
-        <v>114.09191670132206</v>
+        <v>114.0452093217136</v>
       </c>
       <c r="AB189" s="9"/>
       <c r="AC189" s="9"/>
@@ -19620,10 +19612,10 @@
         <v>106.5112001162839</v>
       </c>
       <c r="Z190" s="17">
-        <v>110.15563188788609</v>
+        <v>110.17009604121699</v>
       </c>
       <c r="AA190" s="17">
-        <v>111.96581610013645</v>
+        <v>111.91888125405558</v>
       </c>
       <c r="AB190" s="9"/>
       <c r="AC190" s="9"/>
@@ -19770,10 +19762,10 @@
         <v>137.27497328159745</v>
       </c>
       <c r="Z191" s="17">
-        <v>126.37773927253086</v>
+        <v>126.37773927263814</v>
       </c>
       <c r="AA191" s="17">
-        <v>130.06307975961755</v>
+        <v>130.07412124064098</v>
       </c>
       <c r="AB191" s="9"/>
       <c r="AC191" s="9"/>
@@ -19920,10 +19912,10 @@
         <v>126.72825807148482</v>
       </c>
       <c r="Z192" s="17">
-        <v>137.54823214494155</v>
+        <v>137.54834233113172</v>
       </c>
       <c r="AA192" s="17">
-        <v>144.31972352712293</v>
+        <v>144.31383684142727</v>
       </c>
       <c r="AB192" s="9"/>
       <c r="AC192" s="9"/>
@@ -20070,10 +20062,10 @@
         <v>120.1242039627203</v>
       </c>
       <c r="Z193" s="17">
-        <v>127.1500585132228</v>
+        <v>127.17108278813865</v>
       </c>
       <c r="AA193" s="17">
-        <v>124.03632525294913</v>
+        <v>124.07395616146002</v>
       </c>
       <c r="AB193" s="9"/>
       <c r="AC193" s="9"/>
@@ -20220,10 +20212,10 @@
         <v>115.70673131377302</v>
       </c>
       <c r="Z194" s="17">
-        <v>119.0601224249926</v>
+        <v>119.04952953041597</v>
       </c>
       <c r="AA194" s="17">
-        <v>124.43776326240329</v>
+        <v>124.59850191305333</v>
       </c>
       <c r="AB194" s="9"/>
       <c r="AC194" s="9"/>
@@ -20370,10 +20362,10 @@
         <v>118.92982474788624</v>
       </c>
       <c r="Z195" s="17">
-        <v>118.03445827085253</v>
+        <v>118.01139787018447</v>
       </c>
       <c r="AA195" s="17">
-        <v>123.70993185033817</v>
+        <v>124.02621284306754</v>
       </c>
       <c r="AB195" s="9"/>
       <c r="AC195" s="9"/>
@@ -20520,10 +20512,10 @@
         <v>103.50750135116087</v>
       </c>
       <c r="Z196" s="17">
-        <v>106.2830617054446</v>
+        <v>106.29026863987234</v>
       </c>
       <c r="AA196" s="17">
-        <v>103.98966806465309</v>
+        <v>104.12372935550734</v>
       </c>
       <c r="AB196" s="9"/>
       <c r="AC196" s="9"/>
@@ -20670,10 +20662,10 @@
         <v>118.16355759445145</v>
       </c>
       <c r="Z197" s="17">
-        <v>123.22348431905104</v>
+        <v>123.20976223409002</v>
       </c>
       <c r="AA197" s="17">
-        <v>132.54172595182524</v>
+        <v>132.71014143790418</v>
       </c>
       <c r="AB197" s="9"/>
       <c r="AC197" s="9"/>
@@ -20820,10 +20812,10 @@
         <v>119.21415890458795</v>
       </c>
       <c r="Z198" s="17">
-        <v>123.35520599598865</v>
+        <v>123.35974974426982</v>
       </c>
       <c r="AA198" s="17">
-        <v>123.64893975133722</v>
+        <v>123.70003868677667</v>
       </c>
       <c r="AB198" s="9"/>
       <c r="AC198" s="9"/>
@@ -21065,10 +21057,10 @@
         <v>112.07712346983033</v>
       </c>
       <c r="Z200" s="20">
-        <v>115.79063590261671</v>
+        <v>115.78895213076142</v>
       </c>
       <c r="AA200" s="20">
-        <v>118.26919468268751</v>
+        <v>118.24984771554684</v>
       </c>
       <c r="AB200" s="9"/>
       <c r="AC200" s="9"/>
@@ -21374,7 +21366,7 @@
     </row>
     <row r="207" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="209" spans="1:94" x14ac:dyDescent="0.2">
@@ -21384,7 +21376,7 @@
     </row>
     <row r="210" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="211" spans="1:94" x14ac:dyDescent="0.2">
@@ -21586,10 +21578,10 @@
         <v>14.199506900878333</v>
       </c>
       <c r="Z216" s="20">
-        <v>14.165074362297418</v>
+        <v>14.185352719556748</v>
       </c>
       <c r="AA216" s="20">
-        <v>14.154829152285602</v>
+        <v>14.2047938754807</v>
       </c>
       <c r="AB216" s="9"/>
       <c r="AC216" s="9"/>
@@ -21736,10 +21728,10 @@
         <v>1.017811154410182</v>
       </c>
       <c r="Z217" s="20">
-        <v>0.93179415773343932</v>
+        <v>0.93157741089435264</v>
       </c>
       <c r="AA217" s="20">
-        <v>1.0904703589303451</v>
+        <v>1.0918773562052346</v>
       </c>
       <c r="AB217" s="9"/>
       <c r="AC217" s="9"/>
@@ -21886,10 +21878,10 @@
         <v>2.9090714804664048</v>
       </c>
       <c r="Z218" s="20">
-        <v>2.7107458366622015</v>
+        <v>2.7146462178706687</v>
       </c>
       <c r="AA218" s="20">
-        <v>2.614998864695584</v>
+        <v>2.6273294517143566</v>
       </c>
       <c r="AB218" s="9"/>
       <c r="AC218" s="9"/>
@@ -22036,10 +22028,10 @@
         <v>0.2283488284297191</v>
       </c>
       <c r="Z219" s="20">
-        <v>0.22871336819362126</v>
+        <v>0.23156768701600083</v>
       </c>
       <c r="AA219" s="20">
-        <v>0.27448478679431404</v>
+        <v>0.27959827746830035</v>
       </c>
       <c r="AB219" s="9"/>
       <c r="AC219" s="9"/>
@@ -22186,10 +22178,10 @@
         <v>0.13764472587339516</v>
       </c>
       <c r="Z220" s="20">
-        <v>0.20258509557328536</v>
+        <v>0.20335599959547004</v>
       </c>
       <c r="AA220" s="20">
-        <v>0.20399733860231584</v>
+        <v>0.20433290332413845</v>
       </c>
       <c r="AB220" s="9"/>
       <c r="AC220" s="9"/>
@@ -22336,10 +22328,10 @@
         <v>0.86328718913644631</v>
       </c>
       <c r="Z221" s="20">
-        <v>0.69183541131977866</v>
+        <v>0.69351662661679436</v>
       </c>
       <c r="AA221" s="20">
-        <v>0.79344477563321902</v>
+        <v>0.79583458069524637</v>
       </c>
       <c r="AB221" s="9"/>
       <c r="AC221" s="9"/>
@@ -22486,10 +22478,10 @@
         <v>6.7111704803351895</v>
       </c>
       <c r="Z222" s="20">
-        <v>6.8224647464685813</v>
+        <v>6.815321095348521</v>
       </c>
       <c r="AA222" s="20">
-        <v>6.3360150070920236</v>
+        <v>6.3155864291764594</v>
       </c>
       <c r="AB222" s="9"/>
       <c r="AC222" s="9"/>
@@ -22636,10 +22628,10 @@
         <v>0.29622849461654799</v>
       </c>
       <c r="Z223" s="20">
-        <v>0.33203234949646615</v>
+        <v>0.33230767813238909</v>
       </c>
       <c r="AA223" s="20">
-        <v>0.38066569156989605</v>
+        <v>0.38069855443808998</v>
       </c>
       <c r="AB223" s="9"/>
       <c r="AC223" s="9"/>
@@ -22786,10 +22778,10 @@
         <v>2.0359445476104496</v>
       </c>
       <c r="Z224" s="20">
-        <v>2.2449033968500447</v>
+        <v>2.2630600040825537</v>
       </c>
       <c r="AA224" s="20">
-        <v>2.460752328967907</v>
+        <v>2.5095363224588727</v>
       </c>
       <c r="AB224" s="9"/>
       <c r="AC224" s="9"/>
@@ -22936,10 +22928,10 @@
         <v>16.884866130896629</v>
       </c>
       <c r="Z225" s="20">
-        <v>17.285209168550235</v>
+        <v>17.277538879508089</v>
       </c>
       <c r="AA225" s="20">
-        <v>16.916745970105048</v>
+        <v>16.970385827861676</v>
       </c>
       <c r="AB225" s="9"/>
       <c r="AC225" s="9"/>
@@ -23086,10 +23078,10 @@
         <v>2.8744399534605276</v>
       </c>
       <c r="Z226" s="20">
-        <v>3.3500086695667974</v>
+        <v>3.3477686519800924</v>
       </c>
       <c r="AA226" s="20">
-        <v>2.9393624940382006</v>
+        <v>2.94450889503088</v>
       </c>
       <c r="AB226" s="9"/>
       <c r="AC226" s="9"/>
@@ -23236,10 +23228,10 @@
         <v>1.8088382308754918</v>
       </c>
       <c r="Z227" s="20">
-        <v>1.9040156618834125</v>
+        <v>1.9013087645852449</v>
       </c>
       <c r="AA227" s="20">
-        <v>1.9233304017267285</v>
+        <v>1.9296146989895833</v>
       </c>
       <c r="AB227" s="9"/>
       <c r="AC227" s="9"/>
@@ -23386,10 +23378,10 @@
         <v>6.7457628938507348</v>
       </c>
       <c r="Z228" s="20">
-        <v>6.2344730388630607</v>
+        <v>6.2317370553764517</v>
       </c>
       <c r="AA228" s="20">
-        <v>5.9271613502095395</v>
+        <v>5.9312538967563446</v>
       </c>
       <c r="AB228" s="9"/>
       <c r="AC228" s="9"/>
@@ -23536,10 +23528,10 @@
         <v>5.4558250527098737</v>
       </c>
       <c r="Z229" s="20">
-        <v>5.7967117982369638</v>
+        <v>5.7967244075663</v>
       </c>
       <c r="AA229" s="20">
-        <v>6.1268917241305783</v>
+        <v>6.1650083370848705</v>
       </c>
       <c r="AB229" s="9"/>
       <c r="AC229" s="9"/>
@@ -23686,10 +23678,10 @@
         <v>51.542418033351353</v>
       </c>
       <c r="Z230" s="20">
-        <v>50.684462675794549</v>
+        <v>50.692881420168014</v>
       </c>
       <c r="AA230" s="20">
-        <v>50.334786861286233</v>
+        <v>50.269403434645113</v>
       </c>
       <c r="AB230" s="9"/>
       <c r="AC230" s="9"/>
@@ -23836,10 +23828,10 @@
         <v>45.340900680874299</v>
       </c>
       <c r="Z231" s="20">
-        <v>44.086627196817844</v>
+        <v>44.09717276822883</v>
       </c>
       <c r="AA231" s="20">
-        <v>45.056982850525984</v>
+        <v>45.007286716635377</v>
       </c>
       <c r="AB231" s="9"/>
       <c r="AC231" s="9"/>
@@ -23986,10 +23978,10 @@
         <v>8.29127157957118E-2</v>
       </c>
       <c r="Z232" s="20">
-        <v>0.7477230420287494</v>
+        <v>0.74722731393969477</v>
       </c>
       <c r="AA232" s="20">
-        <v>5.9371512721116314E-2</v>
+        <v>5.9167111777554182E-2</v>
       </c>
       <c r="AB232" s="9"/>
       <c r="AC232" s="9"/>
@@ -24136,10 +24128,10 @@
         <v>4.0549110183344128</v>
       </c>
       <c r="Z233" s="20">
-        <v>5.124549695611468</v>
+        <v>5.1211249210762535</v>
       </c>
       <c r="AA233" s="20">
-        <v>3.3254958946365107</v>
+        <v>3.3142276217560691</v>
       </c>
       <c r="AB233" s="9"/>
       <c r="AC233" s="9"/>
@@ -24286,10 +24278,10 @@
         <v>2.0636936183469241</v>
       </c>
       <c r="Z234" s="20">
-        <v>0.72556274133649012</v>
+        <v>0.72735641692324093</v>
       </c>
       <c r="AA234" s="20">
-        <v>1.8929366034026178</v>
+        <v>1.8887219844761112</v>
       </c>
       <c r="AB234" s="9"/>
       <c r="AC234" s="9"/>
@@ -24436,10 +24428,10 @@
         <v>17.373208934873695</v>
       </c>
       <c r="Z235" s="20">
-        <v>17.865253793357802</v>
+        <v>17.84422698076715</v>
       </c>
       <c r="AA235" s="20">
-        <v>18.593638016323112</v>
+        <v>18.5554168620125</v>
       </c>
       <c r="AB235" s="9"/>
       <c r="AC235" s="9"/>
@@ -24586,10 +24578,10 @@
         <v>1.6125139248574898</v>
       </c>
       <c r="Z236" s="20">
-        <v>1.5741921939462267</v>
+        <v>1.5713919307639621</v>
       </c>
       <c r="AA236" s="20">
-        <v>1.9714839655808409</v>
+        <v>1.9746222860564002</v>
       </c>
       <c r="AB236" s="9"/>
       <c r="AC236" s="9"/>
@@ -24736,10 +24728,10 @@
         <v>2.9045495221362132</v>
       </c>
       <c r="Z237" s="20">
-        <v>3.5107984572539443</v>
+        <v>3.5115896442739465</v>
       </c>
       <c r="AA237" s="20">
-        <v>2.9041722596759976</v>
+        <v>2.906685690280693</v>
       </c>
       <c r="AB237" s="9"/>
       <c r="AC237" s="9"/>
@@ -24886,10 +24878,10 @@
         <v>9.2263236241236495</v>
       </c>
       <c r="Z238" s="20">
-        <v>8.9713324691399539</v>
+        <v>8.9552769970067363</v>
       </c>
       <c r="AA238" s="20">
-        <v>9.925284607203098</v>
+        <v>9.9434818079891727</v>
       </c>
       <c r="AB238" s="9"/>
       <c r="AC238" s="9"/>
@@ -25036,10 +25028,10 @@
         <v>3.6298218637563417</v>
       </c>
       <c r="Z239" s="20">
-        <v>3.8089306730176777</v>
+        <v>3.8059684087225034</v>
       </c>
       <c r="AA239" s="20">
-        <v>3.7926971838631749</v>
+        <v>3.730627077686234</v>
       </c>
       <c r="AB239" s="9"/>
       <c r="AC239" s="9"/>
@@ -25590,7 +25582,7 @@
     </row>
     <row r="248" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="250" spans="1:94" x14ac:dyDescent="0.2">
@@ -25600,7 +25592,7 @@
     </row>
     <row r="251" spans="1:94" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="252" spans="1:94" x14ac:dyDescent="0.2">
@@ -25802,10 +25794,10 @@
         <v>13.623950092408185</v>
       </c>
       <c r="Z257" s="20">
-        <v>13.868267400040438</v>
+        <v>13.893756976117256</v>
       </c>
       <c r="AA257" s="20">
-        <v>13.753655674691274</v>
+        <v>13.798276914522395</v>
       </c>
       <c r="AB257" s="9"/>
       <c r="AC257" s="9"/>
@@ -25952,10 +25944,10 @@
         <v>0.96801726905317798</v>
       </c>
       <c r="Z258" s="20">
-        <v>0.84349566315643165</v>
+        <v>0.84343387408267168</v>
       </c>
       <c r="AA258" s="20">
-        <v>0.93944599131573625</v>
+        <v>0.94275269163118547</v>
       </c>
       <c r="AB258" s="9"/>
       <c r="AC258" s="9"/>
@@ -26102,10 +26094,10 @@
         <v>2.476239772105763</v>
       </c>
       <c r="Z259" s="20">
-        <v>2.4232130334457502</v>
+        <v>2.426745299006051</v>
       </c>
       <c r="AA259" s="20">
-        <v>2.3083835432163595</v>
+        <v>2.326857580352963</v>
       </c>
       <c r="AB259" s="9"/>
       <c r="AC259" s="9"/>
@@ -26252,10 +26244,10 @@
         <v>0.21887533164079925</v>
       </c>
       <c r="Z260" s="20">
-        <v>0.22872373758076975</v>
+        <v>0.23217127540619251</v>
       </c>
       <c r="AA260" s="20">
-        <v>0.25477853661033245</v>
+        <v>0.26110474639671399</v>
       </c>
       <c r="AB260" s="9"/>
       <c r="AC260" s="9"/>
@@ -26402,10 +26394,10 @@
         <v>0.12285725609382989</v>
       </c>
       <c r="Z261" s="20">
-        <v>0.17417111471377716</v>
+        <v>0.17509638249263237</v>
       </c>
       <c r="AA261" s="20">
-        <v>0.16424154008377656</v>
+        <v>0.16495918356532541</v>
       </c>
       <c r="AB261" s="9"/>
       <c r="AC261" s="9"/>
@@ -26552,10 +26544,10 @@
         <v>0.77394835639434678</v>
       </c>
       <c r="Z262" s="20">
-        <v>0.63103532604597956</v>
+        <v>0.63325718427577671</v>
       </c>
       <c r="AA262" s="20">
-        <v>0.69507961976630106</v>
+        <v>0.69910650052545398</v>
       </c>
       <c r="AB262" s="9"/>
       <c r="AC262" s="9"/>
@@ -26702,10 +26694,10 @@
         <v>6.7853252497287189</v>
       </c>
       <c r="Z263" s="20">
-        <v>6.9835033864158902</v>
+        <v>6.9764447755604895</v>
       </c>
       <c r="AA263" s="20">
-        <v>6.6227225260293343</v>
+        <v>6.5852786761221163</v>
       </c>
       <c r="AB263" s="9"/>
       <c r="AC263" s="9"/>
@@ -26852,10 +26844,10 @@
         <v>0.26836298322800123</v>
       </c>
       <c r="Z264" s="20">
-        <v>0.32092132202316698</v>
+        <v>0.32129660932703669</v>
       </c>
       <c r="AA264" s="20">
-        <v>0.33540467407600866</v>
+        <v>0.33588368535023705</v>
       </c>
       <c r="AB264" s="9"/>
       <c r="AC264" s="9"/>
@@ -27002,10 +26994,10 @@
         <v>2.010323874163547</v>
       </c>
       <c r="Z265" s="20">
-        <v>2.2632038166586717</v>
+        <v>2.2853115759664071</v>
       </c>
       <c r="AA265" s="20">
-        <v>2.4335992435934224</v>
+        <v>2.4823338505783994</v>
       </c>
       <c r="AB265" s="9"/>
       <c r="AC265" s="9"/>
@@ -27152,10 +27144,10 @@
         <v>16.258294242238335</v>
       </c>
       <c r="Z266" s="20">
-        <v>16.755431416381697</v>
+        <v>16.746673073219178</v>
       </c>
       <c r="AA266" s="20">
-        <v>16.396713206287565</v>
+        <v>16.469013955418085</v>
       </c>
       <c r="AB266" s="9"/>
       <c r="AC266" s="9"/>
@@ -27302,10 +27294,10 @@
         <v>2.6504922349986733</v>
       </c>
       <c r="Z267" s="20">
-        <v>3.1122182989117944</v>
+        <v>3.1102706425985645</v>
       </c>
       <c r="AA267" s="20">
-        <v>2.6953368106541493</v>
+        <v>2.7026316858523969</v>
       </c>
       <c r="AB267" s="9"/>
       <c r="AC267" s="9"/>
@@ -27452,10 +27444,10 @@
         <v>1.6441114367457994</v>
       </c>
       <c r="Z268" s="20">
-        <v>1.7373642379909766</v>
+        <v>1.735075104600196</v>
       </c>
       <c r="AA268" s="20">
-        <v>1.7274035571272373</v>
+        <v>1.7328344573468373</v>
       </c>
       <c r="AB268" s="9"/>
       <c r="AC268" s="9"/>
@@ -27602,10 +27594,10 @@
         <v>6.2156216554347621</v>
       </c>
       <c r="Z269" s="20">
-        <v>5.6831309105768968</v>
+        <v>5.6787020815096669</v>
       </c>
       <c r="AA269" s="20">
-        <v>5.5713886605480791</v>
+        <v>5.5777910263928661</v>
       </c>
       <c r="AB269" s="9"/>
       <c r="AC269" s="9"/>
@@ -27752,10 +27744,10 @@
         <v>5.7480689150591031</v>
       </c>
       <c r="Z270" s="20">
-        <v>6.22271796890203</v>
+        <v>6.2226252445107484</v>
       </c>
       <c r="AA270" s="20">
-        <v>6.4025841779581025</v>
+        <v>6.4557567858259848</v>
       </c>
       <c r="AB270" s="9"/>
       <c r="AC270" s="9"/>
@@ -27902,10 +27894,10 @@
         <v>53.28952743046581</v>
       </c>
       <c r="Z271" s="20">
-        <v>52.001641598478209</v>
+        <v>52.004067985755718</v>
       </c>
       <c r="AA271" s="20">
-        <v>52.177707928190678</v>
+        <v>52.122744447156713</v>
       </c>
       <c r="AB271" s="9"/>
       <c r="AC271" s="9"/>
@@ -28052,10 +28044,10 @@
         <v>47.710266322187024</v>
       </c>
       <c r="Z272" s="20">
-        <v>46.341875675650464</v>
+        <v>46.346201103901308</v>
       </c>
       <c r="AA272" s="20">
-        <v>47.593571521843039</v>
+        <v>47.553234456042524</v>
       </c>
       <c r="AB272" s="9"/>
       <c r="AC272" s="9"/>
@@ -28202,10 +28194,10 @@
         <v>6.7693465628236804E-2</v>
       </c>
       <c r="Z273" s="20">
-        <v>0.68508367861242903</v>
+        <v>0.68461952383803415</v>
       </c>
       <c r="AA273" s="20">
-        <v>5.3987811218964551E-2</v>
+        <v>5.3788577548955982E-2</v>
       </c>
       <c r="AB273" s="9"/>
       <c r="AC273" s="9"/>
@@ -28352,10 +28344,10 @@
         <v>3.5861201738028163</v>
       </c>
       <c r="Z274" s="20">
-        <v>4.3139403445341538</v>
+        <v>4.3109911634895735</v>
       </c>
       <c r="AA274" s="20">
-        <v>2.7252250196095158</v>
+        <v>2.7156572103196401</v>
       </c>
       <c r="AB274" s="9"/>
       <c r="AC274" s="9"/>
@@ -28502,10 +28494,10 @@
         <v>1.925447468847737</v>
       </c>
       <c r="Z275" s="20">
-        <v>0.66074189968116392</v>
+        <v>0.66225619452681539</v>
       </c>
       <c r="AA275" s="20">
-        <v>1.8049235755191522</v>
+        <v>1.8000642032455798</v>
       </c>
       <c r="AB275" s="9"/>
       <c r="AC275" s="9"/>
@@ -28652,10 +28644,10 @@
         <v>16.828228234887685</v>
       </c>
       <c r="Z276" s="20">
-        <v>17.37465958509965</v>
+        <v>17.355501964907845</v>
       </c>
       <c r="AA276" s="20">
-        <v>17.67192319083048</v>
+        <v>17.609964682902817</v>
       </c>
       <c r="AB276" s="9"/>
       <c r="AC276" s="9"/>
@@ -28802,10 +28794,10 @@
         <v>1.5196013500918375</v>
       </c>
       <c r="Z277" s="20">
-        <v>1.5442669694954698</v>
+        <v>1.5417987443047036</v>
       </c>
       <c r="AA277" s="20">
-        <v>1.884778509304788</v>
+        <v>1.8826567325517247</v>
       </c>
       <c r="AB277" s="9"/>
       <c r="AC277" s="9"/>
@@ -28952,10 +28944,10 @@
         <v>3.1450238018236738</v>
       </c>
       <c r="Z278" s="20">
-        <v>3.8248576900992224</v>
+        <v>3.8254046247765876</v>
       </c>
       <c r="AA278" s="20">
-        <v>3.302963849813755</v>
+        <v>3.3010260231758708</v>
       </c>
       <c r="AB278" s="9"/>
       <c r="AC278" s="9"/>
@@ -29102,10 +29094,10 @@
         <v>8.7510890247779258</v>
       </c>
       <c r="Z279" s="20">
-        <v>8.4301811236391408</v>
+        <v>8.4159089403487499</v>
       </c>
       <c r="AA279" s="20">
-        <v>8.8564971450352505</v>
+        <v>8.8600252913391735</v>
       </c>
       <c r="AB279" s="9"/>
       <c r="AC279" s="9"/>
@@ -29252,10 +29244,10 @@
         <v>3.4125140581942457</v>
       </c>
       <c r="Z280" s="20">
-        <v>3.575353801865814</v>
+        <v>3.5723896554778043</v>
       </c>
       <c r="AA280" s="20">
-        <v>3.6276836866766868</v>
+        <v>3.5662566358360452</v>
       </c>
       <c r="AB280" s="9"/>
       <c r="AC280" s="9"/>
